--- a/output/第10期計画_認定率の年齢調整分析.xlsx
+++ b/output/第10期計画_認定率の年齢調整分析.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>レッドチームレビュー No.1（年齢調整が不十分）に対応するため、見える化システムのB4系列（年齢階級別認定率）、B5系列（調整済み認定率）、B6系列（調整済み重度・軽度認定率）により、認定率の推移を年齢構成の影響を除いて分析する。本分析により、従来の説明「軽度は改善し中重度は悪化している」が誤りであり、実際は「中重度は改善が続き、軽度が直近で悪化に転じている」ことが判明した。作成日：令和8年7月29日。</t>
+          <t>自己点検記録 No.1（年齢調整が不十分）に対応するため、見える化システムのB4系列（年齢階級別認定率）、B5系列（調整済み認定率）、B6系列（調整済み重度・軽度認定率）により、認定率の推移を年齢構成の影響を除いて分析する。本分析により、従来の説明「軽度は改善し中重度は悪化している」が誤りであり、実際は「中重度は改善が続き、軽度が直近で悪化に転じている」ことが判明した。作成日：令和8年7月29日。</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>重点は重度化防止から介護予防（軽度認定の抑制）へ移る。通いの場が同規模保険者の3分の2という調査結果と整合する</t>
+          <t>重点は重度化防止から介護予防（軽度認定の抑制）へ移る。通いの場が同規模保険者の3分の2という調査結果と符合する</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3869,7 +3869,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>注1）単位は％。H30→R7は平成30年3月末から令和7年3月末、R5→R7は令和5年3月末から令和7年3月末までの増減（ポイント）。注2）見える化システムの区分では、重度は要介護3〜5、軽度は要支援1〜要介護2である。注3）本表の最も重要な所見は、中重度の認定率が一貫して低下している一方、軽度の認定率が令和5年を底に上昇に転じていることである。従来の説明「軽度は改善し中重度は悪化している」は逆であった。注4）この訂正により、第10期の施策の重点は重度化防止から介護予防（軽度認定の抑制）へ移る。通いの場の参加率が同規模保険者の3分の2にとどまり、特に男性が3.8％と低いこと（調査クロス集計・分析 19・22シート）と整合する。</t>
+          <t>注1）単位は％。H30→R7は平成30年3月末から令和7年3月末、R5→R7は令和5年3月末から令和7年3月末までの増減（ポイント）。注2）見える化システムの区分では、重度は要介護3〜5、軽度は要支援1〜要介護2である。注3）本表の最も重要な所見は、中重度の認定率が一貫して低下している一方、軽度の認定率が令和5年を底に上昇に転じていることである。従来の説明「軽度は改善し中重度は悪化している」は逆であった。注4）この訂正により、第10期の施策の重点は重度化防止から介護予防（軽度認定の抑制）へ移る。通いの場の参加率が同規模保険者の3分の2にとどまり、特に男性が3.8％と低いこと（調査クロス集計・分析 19・22シート）と符合する。</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>注1）本分析はレッドチームレビュー No.1（年齢調整が不十分）への対応として行った。指摘は的中し、従来の説明の一部が誤りであることが確認された。注2）最も重要な影響は、第10期の施策の重点が重度化防止から介護予防（軽度認定の抑制）へ移ることである。これは調査分析で確認した通いの場の低参加率、特に男性の不参加という所見と整合する。注3）将来推計の前提（保険料と施策評価の他団体比較 06シート No.2）についても、軽度と重度を分けた設定が必要となる。認定者数の推計を要介護度別に行うことを提案する。</t>
+          <t>注1）本分析は自己点検記録 No.1（年齢調整が不十分）への対応として行った。指摘のとおりであることが確認され、従来の説明の一部が誤りであることが確認された。注2）最も重要な影響は、第10期の施策の重点が重度化防止から介護予防（軽度認定の抑制）へ移ることである。これは調査分析で確認した通いの場の低参加率、特に男性の不参加という所見と符合する。注3）将来推計の前提（保険料と施策評価の他団体比較 06シート No.2）についても、軽度と重度を分けた設定が必要となる。認定者数の推計を要介護度別に行うことを提案する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_認定率の年齢調整分析.xlsx
+++ b/output/第10期計画_認定率の年齢調整分析.xlsx
@@ -621,7 +621,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>自己点検記録 No.1（年齢調整が不十分）に対応するため、見える化システムのB4系列（年齢階級別認定率）、B5系列（調整済み認定率）、B6系列（調整済み重度・軽度認定率）により、認定率の推移を年齢構成の影響を除いて分析する。本分析により、従来の説明「軽度は改善し中重度は悪化している」が誤りであり、実際は「中重度は改善が続き、軽度が直近で悪化に転じている」ことが判明した。作成日：令和8年7月29日。</t>
+          <t>受託者の自己点検（年齢調整が不十分）に対応するため、見える化システムのB4系列（年齢階級別認定率）、B5系列（調整済み認定率）、B6系列（調整済み重度・軽度認定率）により、認定率の推移を年齢構成の影響を除いて分析する。本分析により、従来の説明「軽度は改善し中重度は悪化している」が誤りであり、実際は「中重度は改善が続き、軽度が直近で悪化に転じている」ことが判明した。作成日：令和8年7月29日。</t>
         </is>
       </c>
     </row>
@@ -4526,7 +4526,7 @@
     <row r="17" ht="48" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>注1）本分析は自己点検記録 No.1（年齢調整が不十分）への対応として行った。指摘のとおりであることが確認され、従来の説明の一部が誤りであることが確認された。注2）最も重要な影響は、第10期の施策の重点が重度化防止から介護予防（軽度認定の抑制）へ移ることである。これは調査分析で確認した通いの場の低参加率、特に男性の不参加という所見と符合する。注3）将来推計の前提（保険料と施策評価の他団体比較 06シート No.2）についても、軽度と重度を分けた設定が必要となる。認定者数の推計を要介護度別に行うことを提案する。</t>
+          <t>注1）本分析は受託者の自己点検（年齢調整が不十分）への対応として行った。指摘のとおりであることが確認され、従来の説明の一部が誤りであることが確認された。注2）最も重要な影響は、第10期の施策の重点が重度化防止から介護予防（軽度認定の抑制）へ移ることである。これは調査分析で確認した通いの場の低参加率、特に男性の不参加という所見と符合する。注3）将来推計の前提（保険料と施策評価の他団体比較 06シート No.2）についても、軽度と重度を分けた設定が必要となる。認定者数の推計を要介護度別に行うことを提案する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_認定率の年齢調整分析.xlsx
+++ b/output/第10期計画_認定率の年齢調整分析.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>重点は重度化防止から介護予防（軽度認定の抑制）へ移る。通いの場が同規模保険者の3分の2という調査結果と符合する</t>
+          <t>重点は、重度化防止を継続しつつフレイル予防と早期支援の強化へ広がる。軽度認定率は、年齢構成の影響を調整したうえで施策の効果を把握するモニタリング指標とする。通いの場が同規模保険者の3分の2という調査結果と符合する</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3869,7 +3869,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>注1）単位は％。H30→R7は平成30年3月末から令和7年3月末、R5→R7は令和5年3月末から令和7年3月末までの増減（ポイント）。注2）見える化システムの区分では、重度は要介護3〜5、軽度は要支援1〜要介護2である。注3）本表の最も重要な所見は、中重度の認定率が一貫して低下している一方、軽度の認定率が令和5年を底に上昇に転じていることである。従来の説明「軽度は改善し中重度は悪化している」は逆であった。注4）この訂正により、第10期の施策の重点は重度化防止から介護予防（軽度認定の抑制）へ移る。通いの場の参加率が同規模保険者の3分の2にとどまり、特に男性が3.8％と低いこと（調査クロス集計・分析 19・22シート）と符合する。</t>
+          <t>注1）単位は％。H30→R7は平成30年3月末から令和7年3月末、R5→R7は令和5年3月末から令和7年3月末までの増減（ポイント）。注2）見える化システムの区分では、重度は要介護3〜5、軽度は要支援1〜要介護2である。注3）本表の最も重要な所見は、中重度の認定率が一貫して低下している一方、軽度の認定率が令和5年を底に上昇に転じていることである。従来の説明「軽度は改善し中重度は悪化している」は逆であった。注4）この訂正により、第10期の施策の重点は重度化防止を継続しつつフレイル予防と早期支援の強化へ広がる。通いの場の参加率が同規模保険者の3分の2にとどまり、特に男性が3.8％と低いこと（調査クロス集計・分析 19・22シート）と符合する。</t>
         </is>
       </c>
     </row>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="48" customHeight="1">
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>注1）本分析は受託者の自己点検（年齢調整が不十分）への対応として行った。指摘のとおりであることが確認され、従来の説明の一部が誤りであることが確認された。注2）最も重要な影響は、第10期の施策の重点が重度化防止から介護予防（軽度認定の抑制）へ移ることである。これは調査分析で確認した通いの場の低参加率、特に男性の不参加という所見と符合する。注3）将来推計の前提（保険料と施策評価の他団体比較 06シート No.2）についても、軽度と重度を分けた設定が必要となる。認定者数の推計を要介護度別に行うことを提案する。</t>
+          <t>注1）本分析は受託者の自己点検（年齢調整が不十分）への対応として行った。指摘のとおりであることが確認され、従来の説明の一部が誤りであることが確認された。注2）最も重要な影響は、第10期の施策の重点が重度化防止を継続しつつフレイル予防と早期支援の強化へ広がることである。これは調査分析で確認した通いの場の低参加率、特に男性の不参加という所見と符合する。注3）将来推計の前提（保険料と施策評価の他団体比較 06シート No.2）についても、軽度と重度を分けた設定が必要となる。認定者数の推計を要介護度別に行うことを提案する。</t>
         </is>
       </c>
     </row>
